--- a/Documentacion/Producto3/PérezAlcántaraAlejandro_producción_10D_Sprint3.xlsx
+++ b/Documentacion/Producto3/PérezAlcántaraAlejandro_producción_10D_Sprint3.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">SPRINT BACKLOG - SPRINT 3 (31 oct - 20 nov, 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">T47 a T49 se adelantaron el 20 de octubre, antes de que empezara el sprint. Al terminar una tarea se cambia el Estado y se escribe la fecha en Fin; las gráficas se actualizan solas.</t>
+    <t xml:space="preserve">T49 a T51 se adelantaron el 20 de octubre, antes de que empezara el sprint. Al terminar una tarea se cambia el Estado y se escribe la fecha en Fin; las gráficas se actualizan solas.</t>
   </si>
   <si>
     <t xml:space="preserve">TaskID</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Esfuerzo (hrs)</t>
   </si>
   <si>
-    <t xml:space="preserve">T47</t>
+    <t xml:space="preserve">T49</t>
   </si>
   <si>
     <t xml:space="preserve">Preparar el .exe 1.0, el formato de Pruebas Beta y la carpeta para compartir</t>
@@ -126,91 +126,91 @@
     <t xml:space="preserve">Programador</t>
   </si>
   <si>
-    <t xml:space="preserve">T48</t>
+    <t xml:space="preserve">T50</t>
   </si>
   <si>
     <t xml:space="preserve">Diagrama de Gantt del proyecto completo</t>
   </si>
   <si>
-    <t xml:space="preserve">T49</t>
+    <t xml:space="preserve">T51</t>
   </si>
   <si>
     <t xml:space="preserve">Borrador del Postmortem con lo que se sabe hasta ahora</t>
   </si>
   <si>
-    <t xml:space="preserve">T50</t>
+    <t xml:space="preserve">T52</t>
   </si>
   <si>
     <t xml:space="preserve">Probar el .exe en otra computadora (pendiente del Sprint 2, T33)</t>
   </si>
   <si>
-    <t xml:space="preserve">T51</t>
+    <t xml:space="preserve">T53</t>
   </si>
   <si>
     <t xml:space="preserve">Terminar las pruebas Alfa pendientes (PA-09, 10, 11, 13, 14, 16 y 17)</t>
   </si>
   <si>
-    <t xml:space="preserve">T52</t>
+    <t xml:space="preserve">T54</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas Beta cerradas: 3 compañeros del grupo con el formato impreso</t>
   </si>
   <si>
-    <t xml:space="preserve">T53</t>
+    <t xml:space="preserve">T55</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas Beta abiertas: compartir el .zip con más personas</t>
   </si>
   <si>
-    <t xml:space="preserve">T54</t>
+    <t xml:space="preserve">T56</t>
   </si>
   <si>
     <t xml:space="preserve">Capturar los formatos en la hoja Pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T55</t>
+    <t xml:space="preserve">T57</t>
   </si>
   <si>
     <t xml:space="preserve">Pasar los errores de las pruebas al Buglist y darles severidad</t>
   </si>
   <si>
-    <t xml:space="preserve">T56</t>
+    <t xml:space="preserve">T58</t>
   </si>
   <si>
     <t xml:space="preserve">Corregir los bugs de severidad Alta y Media</t>
   </si>
   <si>
-    <t xml:space="preserve">T57</t>
+    <t xml:space="preserve">T59</t>
   </si>
   <si>
     <t xml:space="preserve">Balance de dificultad (vida y daño de enemigos y guardianes) según las pruebas</t>
   </si>
   <si>
-    <t xml:space="preserve">T58</t>
+    <t xml:space="preserve">T60</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas de regresión de las cinco alas con el .exe nuevo</t>
   </si>
   <si>
-    <t xml:space="preserve">T59</t>
+    <t xml:space="preserve">T61</t>
   </si>
   <si>
     <t xml:space="preserve">Compilar la versión corregida después de las pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T60</t>
+    <t xml:space="preserve">T62</t>
   </si>
   <si>
     <t xml:space="preserve">Actualizar el manual y el documento del Producto 3</t>
   </si>
   <si>
-    <t xml:space="preserve">T61</t>
+    <t xml:space="preserve">T63</t>
   </si>
   <si>
     <t xml:space="preserve">Completar el Postmortem con los resultados de las pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T62</t>
+    <t xml:space="preserve">T64</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint Review del Sprint 3</t>
@@ -519,7 +519,7 @@
     <t xml:space="preserve">Pruebas Alfa</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejoras por las pruebas (apuntar, aves, secretos, sonidos, saltar nivel)</t>
+    <t xml:space="preserve">Mejoras por las pruebas (apuntar, aves, secretos, sonidos, saltar nivel, fondos)</t>
   </si>
   <si>
     <t xml:space="preserve">Entrega del Producto 2</t>
@@ -1276,11 +1276,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="81117827"/>
-        <c:axId val="71245625"/>
+        <c:axId val="8118389"/>
+        <c:axId val="85382338"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="81117827"/>
+        <c:axId val="8118389"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1346,7 +1346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71245625"/>
+        <c:crossAx val="85382338"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1354,7 +1354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71245625"/>
+        <c:axId val="85382338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1430,7 +1430,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81117827"/>
+        <c:crossAx val="8118389"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1738,11 +1738,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="97591492"/>
-        <c:axId val="43032375"/>
+        <c:axId val="95485933"/>
+        <c:axId val="80150045"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="97591492"/>
+        <c:axId val="95485933"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1808,7 +1808,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43032375"/>
+        <c:crossAx val="80150045"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1816,7 +1816,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43032375"/>
+        <c:axId val="80150045"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1892,7 +1892,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97591492"/>
+        <c:crossAx val="95485933"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4738,11 +4738,11 @@
         <v>46310</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E13" s="4" t="n">
         <f aca="false">D13-C13+1</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>9</v>

--- a/Documentacion/Producto3/PérezAlcántaraAlejandro_producción_10D_Sprint3.xlsx
+++ b/Documentacion/Producto3/PérezAlcántaraAlejandro_producción_10D_Sprint3.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="190">
   <si>
     <t xml:space="preserve">SPRINT PLAN - ECOS DEL GRIMORIO (al inicio del Sprint 3)</t>
   </si>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">SPRINT BACKLOG - SPRINT 3 (31 oct - 20 nov, 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">T49 a T51 se adelantaron el 20 de octubre, antes de que empezara el sprint. Al terminar una tarea se cambia el Estado y se escribe la fecha en Fin; las gráficas se actualizan solas.</t>
+    <t xml:space="preserve">T50 a T52 se adelantaron el 20 de octubre, antes de que empezara el sprint. Al terminar una tarea se cambia el Estado y se escribe la fecha en Fin; las gráficas se actualizan solas.</t>
   </si>
   <si>
     <t xml:space="preserve">TaskID</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Esfuerzo (hrs)</t>
   </si>
   <si>
-    <t xml:space="preserve">T49</t>
+    <t xml:space="preserve">T50</t>
   </si>
   <si>
     <t xml:space="preserve">Preparar el .exe 1.0, el formato de Pruebas Beta y la carpeta para compartir</t>
@@ -126,91 +126,91 @@
     <t xml:space="preserve">Programador</t>
   </si>
   <si>
-    <t xml:space="preserve">T50</t>
+    <t xml:space="preserve">T51</t>
   </si>
   <si>
     <t xml:space="preserve">Diagrama de Gantt del proyecto completo</t>
   </si>
   <si>
-    <t xml:space="preserve">T51</t>
+    <t xml:space="preserve">T52</t>
   </si>
   <si>
     <t xml:space="preserve">Borrador del Postmortem con lo que se sabe hasta ahora</t>
   </si>
   <si>
-    <t xml:space="preserve">T52</t>
+    <t xml:space="preserve">T53</t>
   </si>
   <si>
     <t xml:space="preserve">Probar el .exe en otra computadora (pendiente del Sprint 2, T33)</t>
   </si>
   <si>
-    <t xml:space="preserve">T53</t>
+    <t xml:space="preserve">T54</t>
   </si>
   <si>
     <t xml:space="preserve">Terminar las pruebas Alfa pendientes (PA-09, 10, 11, 13, 14, 16 y 17)</t>
   </si>
   <si>
-    <t xml:space="preserve">T54</t>
+    <t xml:space="preserve">T55</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas Beta cerradas: 3 compañeros del grupo con el formato impreso</t>
   </si>
   <si>
-    <t xml:space="preserve">T55</t>
+    <t xml:space="preserve">T56</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas Beta abiertas: compartir el .zip con más personas</t>
   </si>
   <si>
-    <t xml:space="preserve">T56</t>
+    <t xml:space="preserve">T57</t>
   </si>
   <si>
     <t xml:space="preserve">Capturar los formatos en la hoja Pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T57</t>
+    <t xml:space="preserve">T58</t>
   </si>
   <si>
     <t xml:space="preserve">Pasar los errores de las pruebas al Buglist y darles severidad</t>
   </si>
   <si>
-    <t xml:space="preserve">T58</t>
+    <t xml:space="preserve">T59</t>
   </si>
   <si>
     <t xml:space="preserve">Corregir los bugs de severidad Alta y Media</t>
   </si>
   <si>
-    <t xml:space="preserve">T59</t>
+    <t xml:space="preserve">T60</t>
   </si>
   <si>
     <t xml:space="preserve">Balance de dificultad (vida y daño de enemigos y guardianes) según las pruebas</t>
   </si>
   <si>
-    <t xml:space="preserve">T60</t>
+    <t xml:space="preserve">T61</t>
   </si>
   <si>
     <t xml:space="preserve">Pruebas de regresión de las cinco alas con el .exe nuevo</t>
   </si>
   <si>
-    <t xml:space="preserve">T61</t>
+    <t xml:space="preserve">T62</t>
   </si>
   <si>
     <t xml:space="preserve">Compilar la versión corregida después de las pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T62</t>
+    <t xml:space="preserve">T63</t>
   </si>
   <si>
     <t xml:space="preserve">Actualizar el manual y el documento del Producto 3</t>
   </si>
   <si>
-    <t xml:space="preserve">T63</t>
+    <t xml:space="preserve">T64</t>
   </si>
   <si>
     <t xml:space="preserve">Completar el Postmortem con los resultados de las pruebas Beta</t>
   </si>
   <si>
-    <t xml:space="preserve">T64</t>
+    <t xml:space="preserve">T65</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint Review del Sprint 3</t>
@@ -520,6 +520,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mejoras por las pruebas (apuntar, aves, secretos, sonidos, saltar nivel, fondos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versión web para celular (GitHub Pages)</t>
   </si>
   <si>
     <t xml:space="preserve">Entrega del Producto 2</t>
@@ -774,83 +777,83 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1069,11 +1072,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1201,11 +1208,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1276,11 +1287,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="8118389"/>
-        <c:axId val="85382338"/>
+        <c:axId val="58649241"/>
+        <c:axId val="40072986"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8118389"/>
+        <c:axId val="58649241"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1346,7 +1357,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85382338"/>
+        <c:crossAx val="40072986"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1354,7 +1365,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85382338"/>
+        <c:axId val="40072986"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1404,7 +1415,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1430,7 +1441,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8118389"/>
+        <c:crossAx val="58649241"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1561,11 +1572,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1663,11 +1678,15 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1738,11 +1757,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="95485933"/>
-        <c:axId val="80150045"/>
+        <c:axId val="98358688"/>
+        <c:axId val="62320860"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="95485933"/>
+        <c:axId val="98358688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1808,7 +1827,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80150045"/>
+        <c:crossAx val="62320860"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1816,7 +1835,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80150045"/>
+        <c:axId val="62320860"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1866,7 +1885,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1892,7 +1911,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95485933"/>
+        <c:crossAx val="98358688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1955,9 +1974,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>4680</xdr:colOff>
+      <xdr:colOff>4320</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>182520</xdr:rowOff>
+      <xdr:rowOff>182160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1965,8 +1984,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="4135680" y="380880"/>
-        <a:ext cx="6119640" cy="3239640"/>
+        <a:off x="4135680" y="379800"/>
+        <a:ext cx="6119280" cy="3231360"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1990,9 +2009,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>507600</xdr:colOff>
+      <xdr:colOff>507240</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>161280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2000,8 +2019,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3430800" y="380880"/>
-        <a:ext cx="5399640" cy="3239640"/>
+        <a:off x="3430800" y="379800"/>
+        <a:ext cx="5399280" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2197,153 +2216,153 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>46266</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <f aca="false">D4-B4+1</f>
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>46283</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" customFormat="false" ht="41.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>46284</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <f aca="false">D5-B5+1</f>
         <v>42</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>46325</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>46326</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">D6-B6+1</f>
         <v>21</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>46346</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>46347</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <f aca="false">D7-B7+1</f>
         <v>10</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>46356</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2396,504 +2415,504 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>46315</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="6" t="n">
         <v>46315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>46315</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>46315</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>46315</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <f aca="false">SUM(G4:G19)</f>
         <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="8" t="str">
+      <c r="G22" s="9" t="str">
         <f aca="false">COUNTIF(F4:F19,"Terminado")&amp;" de "&amp;COUNTA(A4:A19)</f>
         <v>2 de 16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="10" t="n">
         <f aca="false">SUMIF(F4:F19,"Terminado",G4:G19)/G21</f>
         <v>0.0697674418604651</v>
       </c>
@@ -2953,125 +2972,125 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <v>46315</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="6" t="n">
         <v>46326</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>46329</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="6" t="n">
         <v>46331</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="6" t="n">
         <v>46333</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="6" t="n">
         <v>46336</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="6" t="n">
         <v>46338</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="6" t="n">
         <v>46340</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="6" t="n">
         <v>46343</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="6" t="n">
         <v>46345</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3096,210 +3115,210 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <v>46326</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A4)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>43</v>
       </c>
-      <c r="C4" s="12" t="e">
+      <c r="C4" s="13" t="e">
         <f aca="true">IF(A4&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A4))</f>
         <v>#N/A</v>
       </c>
-      <c r="D4" s="12" t="e">
+      <c r="D4" s="13" t="e">
         <f aca="true">IF(A4&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A4))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <v>46329</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A5)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>36.6</v>
       </c>
-      <c r="C5" s="12" t="e">
+      <c r="C5" s="13" t="e">
         <f aca="true">IF(A5&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A5))</f>
         <v>#N/A</v>
       </c>
-      <c r="D5" s="12" t="e">
+      <c r="D5" s="13" t="e">
         <f aca="true">IF(A5&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A5))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>46331</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A6)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>32.3</v>
       </c>
-      <c r="C6" s="12" t="e">
+      <c r="C6" s="13" t="e">
         <f aca="true">IF(A6&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A6))</f>
         <v>#N/A</v>
       </c>
-      <c r="D6" s="12" t="e">
+      <c r="D6" s="13" t="e">
         <f aca="true">IF(A6&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A6))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>46333</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A7)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>28</v>
       </c>
-      <c r="C7" s="12" t="e">
+      <c r="C7" s="13" t="e">
         <f aca="true">IF(A7&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A7))</f>
         <v>#N/A</v>
       </c>
-      <c r="D7" s="12" t="e">
+      <c r="D7" s="13" t="e">
         <f aca="true">IF(A7&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A7))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <v>46336</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A8)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>21.5</v>
       </c>
-      <c r="C8" s="12" t="e">
+      <c r="C8" s="13" t="e">
         <f aca="true">IF(A8&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A8))</f>
         <v>#N/A</v>
       </c>
-      <c r="D8" s="12" t="e">
+      <c r="D8" s="13" t="e">
         <f aca="true">IF(A8&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A8))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <v>46338</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A9)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>17.2</v>
       </c>
-      <c r="C9" s="12" t="e">
+      <c r="C9" s="13" t="e">
         <f aca="true">IF(A9&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A9))</f>
         <v>#N/A</v>
       </c>
-      <c r="D9" s="12" t="e">
+      <c r="D9" s="13" t="e">
         <f aca="true">IF(A9&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A9))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <v>46340</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A10)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>12.9</v>
       </c>
-      <c r="C10" s="12" t="e">
+      <c r="C10" s="13" t="e">
         <f aca="true">IF(A10&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A10))</f>
         <v>#N/A</v>
       </c>
-      <c r="D10" s="12" t="e">
+      <c r="D10" s="13" t="e">
         <f aca="true">IF(A10&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A10))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <v>46343</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A11)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>6.5</v>
       </c>
-      <c r="C11" s="12" t="e">
+      <c r="C11" s="13" t="e">
         <f aca="true">IF(A11&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A11))</f>
         <v>#N/A</v>
       </c>
-      <c r="D11" s="12" t="e">
+      <c r="D11" s="13" t="e">
         <f aca="true">IF(A11&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A11))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <v>46345</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A12)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>2.2</v>
       </c>
-      <c r="C12" s="12" t="e">
+      <c r="C12" s="13" t="e">
         <f aca="true">IF(A12&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A12))</f>
         <v>#N/A</v>
       </c>
-      <c r="D12" s="12" t="e">
+      <c r="D12" s="13" t="e">
         <f aca="true">IF(A12&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A12))</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <v>46346</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <f aca="false">ROUND('Sprint Backlog'!$G$21*('Sprint Plan'!$D$6-A13)/('Sprint Plan'!$D$6-'Sprint Plan'!$B$6),1)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="12" t="e">
+      <c r="C13" s="13" t="e">
         <f aca="true">IF(A13&gt;TODAY(),NA(),'Sprint Backlog'!$G$21-SUMIFS('Sprint Backlog'!$G$4:$G$19,'Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A13))</f>
         <v>#N/A</v>
       </c>
-      <c r="D13" s="12" t="e">
+      <c r="D13" s="13" t="e">
         <f aca="true">IF(A13&gt;TODAY(),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-COUNTIFS('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$I$4:$I$19,"&lt;="&amp;A13))</f>
         <v>#N/A</v>
       </c>
@@ -3333,170 +3352,170 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A4</f>
         <v>46326</v>
       </c>
-      <c r="B4" s="12" t="e">
+      <c r="B4" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D4</f>
         <v>#N/A</v>
       </c>
-      <c r="C4" s="12" t="e">
+      <c r="C4" s="13" t="e">
         <f aca="false">IF(ISNA(B4),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B4)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A5</f>
         <v>46329</v>
       </c>
-      <c r="B5" s="12" t="e">
+      <c r="B5" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D5</f>
         <v>#N/A</v>
       </c>
-      <c r="C5" s="12" t="e">
+      <c r="C5" s="13" t="e">
         <f aca="false">IF(ISNA(B5),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B5)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A6</f>
         <v>46331</v>
       </c>
-      <c r="B6" s="12" t="e">
+      <c r="B6" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D6</f>
         <v>#N/A</v>
       </c>
-      <c r="C6" s="12" t="e">
+      <c r="C6" s="13" t="e">
         <f aca="false">IF(ISNA(B6),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B6)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A7</f>
         <v>46333</v>
       </c>
-      <c r="B7" s="12" t="e">
+      <c r="B7" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D7</f>
         <v>#N/A</v>
       </c>
-      <c r="C7" s="12" t="e">
+      <c r="C7" s="13" t="e">
         <f aca="false">IF(ISNA(B7),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B7)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A8</f>
         <v>46336</v>
       </c>
-      <c r="B8" s="12" t="e">
+      <c r="B8" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D8</f>
         <v>#N/A</v>
       </c>
-      <c r="C8" s="12" t="e">
+      <c r="C8" s="13" t="e">
         <f aca="false">IF(ISNA(B8),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B8)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A9</f>
         <v>46338</v>
       </c>
-      <c r="B9" s="12" t="e">
+      <c r="B9" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D9</f>
         <v>#N/A</v>
       </c>
-      <c r="C9" s="12" t="e">
+      <c r="C9" s="13" t="e">
         <f aca="false">IF(ISNA(B9),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B9)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A10</f>
         <v>46340</v>
       </c>
-      <c r="B10" s="12" t="e">
+      <c r="B10" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D10</f>
         <v>#N/A</v>
       </c>
-      <c r="C10" s="12" t="e">
+      <c r="C10" s="13" t="e">
         <f aca="false">IF(ISNA(B10),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B10)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A11</f>
         <v>46343</v>
       </c>
-      <c r="B11" s="12" t="e">
+      <c r="B11" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D11</f>
         <v>#N/A</v>
       </c>
-      <c r="C11" s="12" t="e">
+      <c r="C11" s="13" t="e">
         <f aca="false">IF(ISNA(B11),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B11)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A12</f>
         <v>46345</v>
       </c>
-      <c r="B12" s="12" t="e">
+      <c r="B12" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D12</f>
         <v>#N/A</v>
       </c>
-      <c r="C12" s="12" t="e">
+      <c r="C12" s="13" t="e">
         <f aca="false">IF(ISNA(B12),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B12)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="12" t="n">
         <f aca="false">'Burn-down Chart'!A13</f>
         <v>46346</v>
       </c>
-      <c r="B13" s="12" t="e">
+      <c r="B13" s="13" t="e">
         <f aca="false">'Burn-down Chart'!D13</f>
         <v>#N/A</v>
       </c>
-      <c r="C13" s="12" t="e">
+      <c r="C13" s="13" t="e">
         <f aca="false">IF(ISNA(B13),NA(),COUNTA('Sprint Backlog'!$A$4:$A$19)-B13)</f>
         <v>#N/A</v>
       </c>
@@ -3529,277 +3548,277 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>46302</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="4"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="4"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="4"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="8" t="str">
+      <c r="E21" s="9" t="str">
         <f aca="false">COUNTIF(E4:E19,"Corregido")&amp;" de "&amp;COUNTA(B4:B19)</f>
         <v>0 de 1</v>
       </c>
@@ -3863,411 +3882,411 @@
   <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="1" t="n">
         <f aca="false">COUNTA(C4:C18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="0" t="str">
+      <c r="H21" s="1" t="str">
         <f aca="false">IF(COUNT(H4:H18)=0,"",ROUND(AVERAGE(H4:H18),1))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="H22" s="0" t="str">
+      <c r="H22" s="1" t="str">
         <f aca="false">IF(COUNT(I4:I18)=0,"",ROUND(AVERAGE(I4:I18),1))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="H23" s="0" t="str">
+      <c r="H23" s="1" t="str">
         <f aca="false">IF(COUNT(J4:J18)=0,"",ROUND(AVERAGE(J4:J18),1))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="1" t="n">
         <f aca="false">COUNTIF(F4:F18,"Terminó el juego")</f>
         <v>0</v>
       </c>
@@ -4340,24 +4359,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="7" style="0" width="4.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="7" style="1" width="4.2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4386,22 +4405,22 @@
       <c r="T3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="17" t="n">
@@ -4448,10 +4467,10 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>154</v>
       </c>
       <c r="C5" s="18" t="n">
@@ -4460,11 +4479,11 @@
       <c r="D5" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <f aca="false">D5-C5+1</f>
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="19"/>
@@ -4483,10 +4502,10 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>155</v>
       </c>
       <c r="C6" s="18" t="n">
@@ -4495,11 +4514,11 @@
       <c r="D6" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <f aca="false">D6-C6+1</f>
         <v>18</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="19"/>
@@ -4518,10 +4537,10 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>156</v>
       </c>
       <c r="C7" s="18" t="n">
@@ -4530,11 +4549,11 @@
       <c r="D7" s="18" t="n">
         <v>46283</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <f aca="false">D7-C7+1</f>
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="19"/>
@@ -4553,10 +4572,10 @@
       <c r="T7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>158</v>
       </c>
       <c r="C8" s="18" t="n">
@@ -4565,11 +4584,11 @@
       <c r="D8" s="18" t="n">
         <v>46295</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <f aca="false">D8-C8+1</f>
         <v>12</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="19"/>
@@ -4588,10 +4607,10 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>159</v>
       </c>
       <c r="C9" s="18" t="n">
@@ -4600,11 +4619,11 @@
       <c r="D9" s="18" t="n">
         <v>46299</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <f aca="false">D9-C9+1</f>
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G9" s="19"/>
@@ -4623,10 +4642,10 @@
       <c r="T9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>160</v>
       </c>
       <c r="C10" s="18" t="n">
@@ -4635,11 +4654,11 @@
       <c r="D10" s="18" t="n">
         <v>46300</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <f aca="false">D10-C10+1</f>
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G10" s="19"/>
@@ -4657,11 +4676,11 @@
       <c r="S10" s="19"/>
       <c r="T10" s="19"/>
     </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>161</v>
       </c>
       <c r="C11" s="18" t="n">
@@ -4670,11 +4689,11 @@
       <c r="D11" s="18" t="n">
         <v>46308</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <f aca="false">D11-C11+1</f>
         <v>7</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G11" s="19"/>
@@ -4693,10 +4712,10 @@
       <c r="T11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>162</v>
       </c>
       <c r="C12" s="18" t="n">
@@ -4705,11 +4724,11 @@
       <c r="D12" s="18" t="n">
         <v>46325</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <f aca="false">D12-C12+1</f>
         <v>24</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G12" s="19"/>
@@ -4727,11 +4746,11 @@
       <c r="S12" s="19"/>
       <c r="T12" s="19"/>
     </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>163</v>
       </c>
       <c r="C13" s="18" t="n">
@@ -4740,11 +4759,11 @@
       <c r="D13" s="18" t="n">
         <v>46316</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <f aca="false">D13-C13+1</f>
         <v>7</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G13" s="19"/>
@@ -4763,24 +4782,24 @@
       <c r="T13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>164</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>46325</v>
+        <v>46317</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>46325</v>
-      </c>
-      <c r="E14" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <f aca="false">D14-C14+1</f>
         <v>1</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>17</v>
+      <c r="F14" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
@@ -4798,23 +4817,23 @@
       <c r="T14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="C15" s="18" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>46333</v>
-      </c>
-      <c r="E15" s="4" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <f aca="false">D15-C15+1</f>
-        <v>8</v>
-      </c>
-      <c r="F15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G15" s="19"/>
@@ -4833,23 +4852,23 @@
       <c r="T15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>167</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>46329</v>
+        <v>46326</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>46338</v>
-      </c>
-      <c r="E16" s="4" t="n">
+        <v>46333</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <f aca="false">D16-C16+1</f>
-        <v>10</v>
-      </c>
-      <c r="F16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="19"/>
@@ -4868,23 +4887,23 @@
       <c r="T16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="A17" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>168</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>46331</v>
+        <v>46329</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>46343</v>
-      </c>
-      <c r="E17" s="4" t="n">
+        <v>46338</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <f aca="false">D17-C17+1</f>
-        <v>13</v>
-      </c>
-      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G17" s="19"/>
@@ -4903,24 +4922,24 @@
       <c r="T17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="A18" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>169</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>46315</v>
+        <v>46331</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>46346</v>
-      </c>
-      <c r="E18" s="4" t="n">
+        <v>46343</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <f aca="false">D18-C18+1</f>
-        <v>32</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
@@ -4938,24 +4957,24 @@
       <c r="T18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="A19" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>46346</v>
+        <v>46315</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>46346</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <f aca="false">D19-C19+1</f>
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>17</v>
+        <v>32</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -4973,23 +4992,23 @@
       <c r="T19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>172</v>
-      </c>
       <c r="C20" s="18" t="n">
-        <v>46347</v>
+        <v>46346</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>46353</v>
-      </c>
-      <c r="E20" s="4" t="n">
+        <v>46346</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <f aca="false">D20-C20+1</f>
-        <v>7</v>
-      </c>
-      <c r="F20" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="19"/>
@@ -5008,23 +5027,23 @@
       <c r="T20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="7" t="s">
+      <c r="A21" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>173</v>
       </c>
       <c r="C21" s="18" t="n">
         <v>46347</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>46355</v>
-      </c>
-      <c r="E21" s="4" t="n">
+        <v>46353</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <f aca="false">D21-C21+1</f>
-        <v>9</v>
-      </c>
-      <c r="F21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="19"/>
@@ -5043,23 +5062,23 @@
       <c r="T21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>174</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>46356</v>
+        <v>46347</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>46356</v>
-      </c>
-      <c r="E22" s="4" t="n">
+        <v>46355</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <f aca="false">D22-C22+1</f>
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="19"/>
@@ -5077,13 +5096,48 @@
       <c r="S22" s="19"/>
       <c r="T22" s="19"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>175</v>
       </c>
+      <c r="C23" s="18" t="n">
+        <v>46356</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <f aca="false">D23-C23+1</f>
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="14" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:T22">
+  <conditionalFormatting sqref="G5:T23">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>AND(AND(G$4&lt;=$D5,G$4+6&gt;=$C5),$F5="Terminado")</formula>
     </cfRule>
@@ -5099,7 +5153,7 @@
       <formula>AND(TODAY()&gt;=G$4,TODAY()&lt;=G$4+6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F22">
+  <conditionalFormatting sqref="F5:F23">
     <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Terminado"</formula>
     </cfRule>
@@ -5126,7 +5180,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F22" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F23" type="list">
       <formula1>"Terminado,En desarrollo,Planeado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5149,90 +5203,90 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="95"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="B3" s="7" t="s">
         <v>178</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="B4" s="7" t="str">
+        <v>180</v>
+      </c>
+      <c r="B4" s="8" t="str">
         <f aca="false">COUNTIF('Sprint Backlog'!$F$4:$F$19,"Terminado")&amp;" de "&amp;COUNTA('Sprint Backlog'!$A$4:$A$19)</f>
         <v>2 de 16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="7" t="str">
+        <v>181</v>
+      </c>
+      <c r="B5" s="8" t="str">
         <f aca="false">SUMIF('Sprint Backlog'!$F$4:$F$19,"Terminado",'Sprint Backlog'!$G$4:$G$19)&amp;" de "&amp;'Sprint Backlog'!$G$21&amp;" hrs"</f>
         <v>3 de 43 hrs</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="7" t="n">
+        <v>182</v>
+      </c>
+      <c r="B6" s="8" t="n">
         <f aca="false">'Pruebas Beta'!H20</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="7" t="str">
+        <v>183</v>
+      </c>
+      <c r="B7" s="8" t="str">
         <f aca="false">Buglist!E21</f>
         <v>0 de 1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="B8" s="7"/>
+        <v>184</v>
+      </c>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="7"/>
+        <v>185</v>
+      </c>
+      <c r="B9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="7"/>
+        <v>186</v>
+      </c>
+      <c r="B10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B11" s="7"/>
+        <v>187</v>
+      </c>
+      <c r="B11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="7" t="s">
         <v>188</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
